--- a/output/pdf_financials_xlsx/GOGO.xlsx
+++ b/output/pdf_financials_xlsx/GOGO.xlsx
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.384024</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.384024</v>
       </c>
     </row>
     <row r="93">
@@ -2560,7 +2560,11 @@
           <t>Warrant reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>1.661293</v>
       </c>
@@ -2584,7 +2588,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>1.722731</v>
       </c>

--- a/output/pdf_financials_xlsx/GOGO.xlsx
+++ b/output/pdf_financials_xlsx/GOGO.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.080378</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000675</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.676829</v>
+        <v>0.596451</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.9852300000000001</v>
+        <v>-0.985905</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.676829</v>
+        <v>0.596451</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9852300000000001</v>
+        <v>-0.985905</v>
       </c>
     </row>
     <row r="30">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>32.65080571866323</v>
+        <v>28.77330274220283</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>220.5658151306407</v>
+        <v>220.7169290078199</v>
       </c>
     </row>
     <row r="31">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">

--- a/output/pdf_financials_xlsx/GOGO.xlsx
+++ b/output/pdf_financials_xlsx/GOGO.xlsx
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.265784</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.348611</v>
       </c>
     </row>
     <row r="65">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.071239</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.032586</v>
       </c>
     </row>
     <row r="68">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>2.799244</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>4.261972</v>
       </c>
     </row>
     <row r="116">
@@ -3046,7 +3046,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>2.799244</v>
       </c>
